--- a/data/RGC_wheel_source_data.xlsx
+++ b/data/RGC_wheel_source_data.xlsx
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>2</v>
       </c>
       <c r="G22" s="17" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>2</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>2</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>2</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="17" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="17" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="17" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="17" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="17" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="17" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="17" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="17" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="17" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>2</v>
       </c>
       <c r="G38" s="17" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>3</v>
       </c>
       <c r="G39" s="17" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>3</v>
       </c>
       <c r="G40" s="17" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>3</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>3</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>3</v>
       </c>
       <c r="G43" s="17" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="G44" s="17" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>3</v>
       </c>
       <c r="G45" s="17" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>3</v>
       </c>
       <c r="G46" s="17" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>3</v>
       </c>
       <c r="G47" s="17" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>3</v>
       </c>
       <c r="G48" s="17" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>3</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>3</v>
       </c>
       <c r="G50" s="17" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>3</v>
       </c>
       <c r="G51" s="17" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>3</v>
       </c>
       <c r="G52" s="17" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>3</v>
       </c>
       <c r="G53" s="17" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>3</v>
       </c>
       <c r="G54" s="17" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>3</v>
       </c>
       <c r="G55" s="17" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>3</v>
       </c>
       <c r="G56" s="17" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>3</v>
       </c>
       <c r="G57" s="17" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>3</v>
       </c>
       <c r="G58" s="17" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>3</v>
       </c>
       <c r="G59" s="17" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>3</v>
       </c>
       <c r="G60" s="17" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>3</v>
       </c>
       <c r="G61" s="17" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>3</v>
       </c>
       <c r="G62" s="17" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>3</v>
       </c>
       <c r="G63" s="17" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>3</v>
       </c>
       <c r="G64" s="17" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>3</v>
       </c>
       <c r="G65" s="17" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>3</v>
       </c>
       <c r="G66" s="17" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>3</v>
       </c>
       <c r="G67" s="17" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>3</v>
       </c>
       <c r="G68" s="17" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>3</v>
       </c>
       <c r="G69" s="17" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         <v>3</v>
       </c>
       <c r="G70" s="17" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>3</v>
       </c>
       <c r="G71" s="17" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>3</v>
       </c>
       <c r="G72" s="17" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>3</v>
       </c>
       <c r="G73" s="17" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>3</v>
       </c>
       <c r="G74" s="17" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>2</v>
       </c>
       <c r="G75" s="17" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>2</v>
       </c>
       <c r="G76" s="17" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>3</v>
       </c>
       <c r="G77" s="17" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>3</v>
       </c>
       <c r="G78" s="17" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>2</v>
       </c>
       <c r="G79" s="17" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="17" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="17" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="17" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="17" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="17" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="17" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="17" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="17" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="17" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="17" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="17" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="17" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="17" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="17" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="17" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="17" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="17" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="17" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="17" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="17" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="17" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="17" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="17" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="17" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="17" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="17" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="17" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="17" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="17" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="17" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="17" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="17" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="17" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="17" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="17" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="17" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="17" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="17" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="17" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="17" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="17" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="17" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="17" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="17" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="17" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="17" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="17" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="17" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="17" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="17" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="17" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="17" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="17" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="17" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="17" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="17" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
     </row>
     <row r="62" ht="56" customHeight="1">
       <c r="A62" s="17" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="17" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="17" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
     </row>
     <row r="65" ht="56" customHeight="1">
       <c r="A65" s="17" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
     </row>
     <row r="66" ht="56" customHeight="1">
       <c r="A66" s="17" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
